--- a/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 20,99</t>
+          <t>-1,81; 21,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 10,34</t>
+          <t>-12,79; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,42; 66,05</t>
+          <t>50,07; 65,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 18,76</t>
+          <t>-2,54; 18,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 7,78</t>
+          <t>-14,08; 8,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,33; 61,91</t>
+          <t>46,1; 62,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 16,92</t>
+          <t>1,38; 16,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 5,5</t>
+          <t>-9,95; 6,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,02; 61,52</t>
+          <t>50,05; 61,55</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 65,47</t>
+          <t>-4,7; 66,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 31,51</t>
+          <t>-31,42; 25,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112,92; 223,07</t>
+          <t>113,25; 217,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 51,87</t>
+          <t>-5,46; 49,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 21,46</t>
+          <t>-30,09; 22,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,25; 177,29</t>
+          <t>94,04; 178,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 47,4</t>
+          <t>3,36; 45,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 15,69</t>
+          <t>-23,07; 16,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>111,0; 176,96</t>
+          <t>110,18; 177,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 23,15</t>
+          <t>3,11; 22,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 16,85</t>
+          <t>-1,78; 16,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,34; 64,1</t>
+          <t>50,51; 64,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 18,29</t>
+          <t>-0,07; 18,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 12,1</t>
+          <t>-5,56; 13,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,9; 60,21</t>
+          <t>45,85; 60,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 17,01</t>
+          <t>4,42; 17,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 12,11</t>
+          <t>-0,98; 11,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,4; 60,32</t>
+          <t>49,62; 60,09</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 68,93</t>
+          <t>7,8; 68,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 49,92</t>
+          <t>-3,74; 50,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112,7; 201,25</t>
+          <t>112,32; 203,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 49,23</t>
+          <t>-0,13; 51,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 33,15</t>
+          <t>-11,92; 36,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68; 172,27</t>
+          <t>95,35; 172,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 47,21</t>
+          <t>10,68; 49,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 33,58</t>
+          <t>-2,28; 31,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>114,01; 171,53</t>
+          <t>111,48; 169,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 14,54</t>
+          <t>-7,26; 14,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 5,69</t>
+          <t>-14,83; 4,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,18; 61,68</t>
+          <t>45,45; 61,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 10,59</t>
+          <t>-9,3; 12,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 4,69</t>
+          <t>-15,42; 5,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,9; 54,51</t>
+          <t>38,29; 54,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 9,35</t>
+          <t>-6,74; 8,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 2,12</t>
+          <t>-12,01; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,42; 55,49</t>
+          <t>44,13; 55,69</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 40,42</t>
+          <t>-15,69; 40,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 15,14</t>
+          <t>-31,32; 13,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,75; 179,56</t>
+          <t>90,95; 174,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 27,09</t>
+          <t>-18,32; 30,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 11,14</t>
+          <t>-29,37; 12,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,32; 138,33</t>
+          <t>70,08; 136,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 23,08</t>
+          <t>-13,35; 21,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 5,4</t>
+          <t>-24,34; 6,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89,2; 139,54</t>
+          <t>88,41; 140,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 12,25</t>
+          <t>-7,04; 12,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 16,16</t>
+          <t>-2,02; 15,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,7; 60,09</t>
+          <t>45,1; 59,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 13,12</t>
+          <t>-5,56; 12,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 5,46</t>
+          <t>-13,65; 3,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,67; 60,23</t>
+          <t>46,39; 60,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 9,08</t>
+          <t>-3,89; 8,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,26</t>
+          <t>-5,4; 7,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,91; 57,61</t>
+          <t>47,82; 58,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 33,59</t>
+          <t>-15,68; 33,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 44,66</t>
+          <t>-4,7; 44,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,22; 174,39</t>
+          <t>96,71; 173,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 34,76</t>
+          <t>-11,87; 36,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 14,42</t>
+          <t>-29,77; 10,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,59; 169,56</t>
+          <t>98,97; 174,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 23,99</t>
+          <t>-8,83; 23,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 19,23</t>
+          <t>-12,33; 19,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105,89; 154,67</t>
+          <t>104,5; 159,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,01</t>
+          <t>1,3; 11,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,43</t>
+          <t>-2,2; 7,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,31; 59,17</t>
+          <t>51,67; 59,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,25</t>
+          <t>-0,08; 9,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,11</t>
+          <t>-6,51; 3,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,92; 55,59</t>
+          <t>48,12; 55,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,48</t>
+          <t>2,43; 9,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,7</t>
+          <t>-3,34; 3,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,08; 55,96</t>
+          <t>50,57; 56,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,2; 32,59</t>
+          <t>3,02; 31,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 19,49</t>
+          <t>-5,32; 21,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118,3; 163,26</t>
+          <t>119,88; 162,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,67; 25,45</t>
+          <t>-0,18; 24,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 7,59</t>
+          <t>-14,91; 7,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>103,22; 139,85</t>
+          <t>104,49; 141,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,71; 23,8</t>
+          <t>5,42; 24,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,45</t>
+          <t>-7,67; 9,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>116,95; 142,41</t>
+          <t>115,41; 144,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 21,71</t>
+          <t>-1,66; 21,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 8,25</t>
+          <t>-13,12; 10,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,07; 65,8</t>
+          <t>49,88; 66,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 18,27</t>
+          <t>-2,77; 18,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 8,69</t>
+          <t>-13,29; 8,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,1; 62,54</t>
+          <t>45,39; 61,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 16,32</t>
+          <t>1,33; 16,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 6,0</t>
+          <t>-10,15; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,05; 61,55</t>
+          <t>49,92; 61,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 66,39</t>
+          <t>-3,89; 68,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 25,57</t>
+          <t>-30,59; 34,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113,25; 217,58</t>
+          <t>111,75; 223,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 49,19</t>
+          <t>-6,76; 48,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 22,62</t>
+          <t>-29,15; 23,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,04; 178,94</t>
+          <t>91,98; 174,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 45,66</t>
+          <t>3,1; 45,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 16,27</t>
+          <t>-23,62; 13,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>110,18; 177,59</t>
+          <t>109,55; 175,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 22,71</t>
+          <t>3,51; 22,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 16,21</t>
+          <t>-1,28; 17,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,51; 64,71</t>
+          <t>50,06; 64,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 18,2</t>
+          <t>-0,72; 18,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 13,02</t>
+          <t>-5,54; 12,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,85; 60,34</t>
+          <t>45,5; 60,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 17,92</t>
+          <t>4,57; 18,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 11,29</t>
+          <t>-1,71; 11,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,62; 60,09</t>
+          <t>49,69; 60,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 68,02</t>
+          <t>8,4; 69,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 50,53</t>
+          <t>-3,51; 51,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112,32; 203,5</t>
+          <t>113,11; 203,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 51,09</t>
+          <t>-1,07; 50,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 36,17</t>
+          <t>-12,15; 35,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35; 172,76</t>
+          <t>96,93; 175,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 49,41</t>
+          <t>10,73; 50,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 31,94</t>
+          <t>-3,89; 29,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>111,48; 169,95</t>
+          <t>111,41; 168,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 14,95</t>
+          <t>-6,85; 15,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 4,93</t>
+          <t>-14,83; 5,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,45; 61,4</t>
+          <t>45,36; 60,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 12,18</t>
+          <t>-11,32; 11,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 5,33</t>
+          <t>-14,33; 5,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,29; 54,75</t>
+          <t>38,36; 55,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 8,68</t>
+          <t>-6,07; 9,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 2,7</t>
+          <t>-12,44; 2,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,13; 55,69</t>
+          <t>43,92; 55,59</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 40,33</t>
+          <t>-14,49; 42,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 13,93</t>
+          <t>-31,86; 14,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,95; 174,12</t>
+          <t>90,55; 170,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 30,55</t>
+          <t>-20,91; 26,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 12,83</t>
+          <t>-27,72; 14,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,08; 136,26</t>
+          <t>71,63; 141,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 21,73</t>
+          <t>-12,4; 22,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 6,42</t>
+          <t>-25,03; 5,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,41; 140,68</t>
+          <t>87,46; 141,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 12,06</t>
+          <t>-7,5; 12,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 15,89</t>
+          <t>-3,52; 15,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,1; 59,72</t>
+          <t>45,09; 59,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 12,98</t>
+          <t>-5,7; 12,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 3,98</t>
+          <t>-13,35; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,39; 60,42</t>
+          <t>45,9; 59,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 8,91</t>
+          <t>-3,74; 9,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 7,68</t>
+          <t>-5,48; 7,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,82; 58,36</t>
+          <t>47,77; 57,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 33,46</t>
+          <t>-16,39; 34,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 44,68</t>
+          <t>-7,89; 42,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96,71; 173,4</t>
+          <t>96,98; 173,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 36,34</t>
+          <t>-12,09; 33,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 10,05</t>
+          <t>-28,78; 13,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,97; 174,99</t>
+          <t>95,66; 164,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 23,19</t>
+          <t>-8,45; 26,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 19,59</t>
+          <t>-12,09; 19,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>104,5; 159,44</t>
+          <t>105,01; 156,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,69</t>
+          <t>1,66; 11,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,93</t>
+          <t>-1,93; 7,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,67; 59,09</t>
+          <t>51,66; 59,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,98</t>
+          <t>0,74; 10,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,05</t>
+          <t>-6,86; 3,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,12; 55,69</t>
+          <t>48,09; 55,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,85</t>
+          <t>2,51; 9,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,85</t>
+          <t>-3,24; 3,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50,57; 56,07</t>
+          <t>51,03; 56,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,02; 31,24</t>
+          <t>4,02; 31,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 21,54</t>
+          <t>-4,77; 21,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119,88; 162,57</t>
+          <t>119,96; 163,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 24,89</t>
+          <t>1,49; 26,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 7,42</t>
+          <t>-15,01; 8,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>104,49; 141,65</t>
+          <t>103,95; 140,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,75</t>
+          <t>5,73; 24,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 9,79</t>
+          <t>-7,53; 9,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>115,41; 144,12</t>
+          <t>117,79; 146,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58,1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,14</t>
+          <t>58,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>56,01</t>
+          <t>56,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 21,7</t>
+          <t>-2,37; 18,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 10,73</t>
+          <t>-14,04; 7,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,88; 66,51</t>
+          <t>45,27; 61,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 18,6</t>
+          <t>-1,94; 20,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 8,83</t>
+          <t>-12,76; 10,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,39; 61,67</t>
+          <t>50,54; 66,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 16,6</t>
+          <t>0,84; 16,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 5,07</t>
+          <t>-9,97; 5,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,92; 61,54</t>
+          <t>50,42; 61,79</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-6,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>129,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>25,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-5,72%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>155,41%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-6,56%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128,68%</t>
+          <t>156,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140,51%</t>
+          <t>141,05%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 68,88</t>
+          <t>-4,94; 51,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 34,13</t>
+          <t>-28,73; 21,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111,75; 223,15</t>
+          <t>91,07; 175,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 48,81</t>
+          <t>-4,33; 65,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 23,14</t>
+          <t>-30,05; 31,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,98; 174,12</t>
+          <t>113,92; 224,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 45,84</t>
+          <t>1,87; 47,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 13,92</t>
+          <t>-23,57; 15,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>109,55; 175,95</t>
+          <t>111,27; 177,9</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53,25</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,24</t>
+          <t>57,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>55,27</t>
+          <t>55,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 22,67</t>
+          <t>-0,38; 18,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 17,37</t>
+          <t>-5,41; 12,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,06; 64,44</t>
+          <t>45,95; 60,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 18,1</t>
+          <t>3,63; 23,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 12,53</t>
+          <t>-1,37; 16,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,5; 60,14</t>
+          <t>50,51; 64,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 18,04</t>
+          <t>3,71; 17,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 11,07</t>
+          <t>-0,96; 12,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,69; 60,05</t>
+          <t>50,55; 60,32</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>129,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>33,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>150,65%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>129,03%</t>
+          <t>151,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138,64%</t>
+          <t>138,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 69,83</t>
+          <t>-0,75; 49,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 51,99</t>
+          <t>-11,77; 33,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113,11; 203,2</t>
+          <t>95,9; 170,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 50,61</t>
+          <t>8,36; 68,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 35,35</t>
+          <t>-2,98; 49,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,93; 175,28</t>
+          <t>112,84; 201,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 50,06</t>
+          <t>8,73; 47,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 29,89</t>
+          <t>-2,19; 33,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>111,41; 168,55</t>
+          <t>113,96; 171,46</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,53</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,98</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>53,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,53</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,88</t>
+          <t>52,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,04</t>
+          <t>49,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 15,32</t>
+          <t>-11,24; 10,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 5,31</t>
+          <t>-15,31; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,36; 60,95</t>
+          <t>38,61; 54,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 11,02</t>
+          <t>-6,81; 14,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 5,83</t>
+          <t>-15,17; 5,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,36; 55,1</t>
+          <t>43,81; 60,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 9,39</t>
+          <t>-4,95; 9,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 2,29</t>
+          <t>-12,04; 2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,92; 55,59</t>
+          <t>43,73; 55,1</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-0,02%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>99,98%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-11,74%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>125,58%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-9,67%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>100,06%</t>
+          <t>123,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>111,99%</t>
+          <t>110,68%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 42,29</t>
+          <t>-21,03; 27,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 14,09</t>
+          <t>-29,95; 11,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,55; 170,69</t>
+          <t>72,09; 138,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 26,98</t>
+          <t>-14,11; 40,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 14,71</t>
+          <t>-31,05; 15,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,63; 141,46</t>
+          <t>89,09; 178,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 22,46</t>
+          <t>-10,38; 23,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 5,9</t>
+          <t>-24,63; 5,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,46; 141,01</t>
+          <t>87,66; 137,95</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53,19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6,09</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>52,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,38</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,3</t>
+          <t>52,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53,0</t>
+          <t>52,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 12,08</t>
+          <t>-6,76; 13,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 15,03</t>
+          <t>-12,53; 5,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,09; 59,66</t>
+          <t>46,48; 60,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 12,42</t>
+          <t>-6,82; 12,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 4,95</t>
+          <t>-3,0; 16,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,9; 59,41</t>
+          <t>44,55; 59,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 9,79</t>
+          <t>-4,46; 9,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 7,2</t>
+          <t>-5,54; 7,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,77; 57,98</t>
+          <t>47,62; 57,43</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-10,46%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127,14%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>14,97%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>129,41%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-10,46%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>127,4%</t>
+          <t>128,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128,56%</t>
+          <t>128,05%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 34,37</t>
+          <t>-14,11; 34,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 42,91</t>
+          <t>-27,28; 14,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96,98; 173,71</t>
+          <t>97,75; 169,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 33,35</t>
+          <t>-15,03; 33,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 13,04</t>
+          <t>-6,67; 44,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,66; 164,5</t>
+          <t>94,59; 173,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 26,56</t>
+          <t>-9,91; 23,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 19,28</t>
+          <t>-12,34; 19,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105,01; 156,96</t>
+          <t>105,16; 154,43</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>51,97</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,62</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>55,36</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,97</t>
+          <t>55,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53,62</t>
+          <t>53,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,84</t>
+          <t>0,78; 10,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 7,82</t>
+          <t>-6,55; 3,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,66; 59,35</t>
+          <t>48,03; 55,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 10,59</t>
+          <t>2,14; 12,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,39</t>
+          <t>-2,49; 7,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,09; 55,62</t>
+          <t>50,96; 58,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,75</t>
+          <t>2,46; 9,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,72</t>
+          <t>-3,25; 3,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,03; 56,55</t>
+          <t>50,87; 55,9</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-4,01%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>121,42%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,27%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>139,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-4,01%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>121,43%</t>
+          <t>138,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>129,77%</t>
+          <t>129,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,02; 31,91</t>
+          <t>1,67; 25,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,29</t>
+          <t>-14,48; 7,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119,96; 163,23</t>
+          <t>103,51; 140,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,49; 26,05</t>
+          <t>5,2; 32,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 8,38</t>
+          <t>-5,99; 19,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>103,95; 140,02</t>
+          <t>117,52; 162,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,73; 24,53</t>
+          <t>5,71; 23,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,24</t>
+          <t>-7,52; 9,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>117,79; 146,31</t>
+          <t>116,91; 142,37</t>
         </is>
       </c>
     </row>
